--- a/Outputs/Scenarios/PtX_demand_LU_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LU_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>3.274988082656695e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>1.486825067883568e-05</v>
+        <v>1.734629245864163e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.956083559611892e-06</v>
+        <v>5.203887737592489e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1370,7 +1370,7 @@
         <v>1.588659768611818e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>9.743020561730945e-05</v>
+        <v>9.743020561730947e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>4.718703464600818e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>4.956083559611892e-06</v>
+        <v>2.230237601825352e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>4.848221138366855e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>7.444074701383709e-05</v>
+        <v>8.684753818280995e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.48135823379457e-05</v>
+        <v>2.605426145484299e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>2.551695335982555e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>2.48135823379457e-05</v>
+        <v>1.116611205207557e-05</v>
       </c>
     </row>
     <row r="43">
